--- a/artfynd/A 63366-2023 artfynd.xlsx
+++ b/artfynd/A 63366-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63366-2023 artfynd.xlsx
+++ b/artfynd/A 63366-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113803876</v>
+        <v>114438030</v>
       </c>
       <c r="B2" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,49 +686,48 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 63366, Lundaborg, Sm</t>
+          <t>A 63336, Lundaborg, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570036</v>
+        <v>570199</v>
       </c>
       <c r="R2" t="n">
-        <v>6409713</v>
+        <v>6409650</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,12 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-12-31</t>
+          <t>2024-01-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-12-31</t>
+          <t>2024-01-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,6 +765,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,49 +784,44 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113803870</v>
+        <v>113803876</v>
       </c>
       <c r="B3" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -903,15 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114438030</v>
+        <v>113803870</v>
       </c>
       <c r="B4" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,26 +926,27 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 63336, Lundaborg, Sm</t>
+          <t>A 63366, Lundaborg, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570199</v>
+        <v>570036</v>
       </c>
       <c r="R4" t="n">
-        <v>6409650</v>
+        <v>6409713</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,12 +970,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2023-12-31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2023-12-31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,7 +984,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1017,15 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114437898</v>
+        <v>114437876</v>
       </c>
       <c r="B5" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,7 +1032,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1069,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570181</v>
+        <v>570186</v>
       </c>
       <c r="R5" t="n">
-        <v>6409538</v>
+        <v>6409519</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,15 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114437921</v>
+        <v>114437898</v>
       </c>
       <c r="B6" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,7 +1142,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1184,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570199</v>
+        <v>570181</v>
       </c>
       <c r="R6" t="n">
-        <v>6409566</v>
+        <v>6409538</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,6 +1219,116 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>114437921</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 63366, Lundaborg, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>570199</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6409566</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-01-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-01-28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
